--- a/config/data/LightCone.xlsx
+++ b/config/data/LightCone.xlsx
@@ -1,115 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="LightCone" sheetId="1" r:id="rId1"/>
+    <sheet name="LightCone" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>LightCone</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>map</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>9de39463d2f7c2f7</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>rarity</t>
-  </si>
-  <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>applicability</t>
-  </si>
-  <si>
-    <t>passive_rule_identity_id</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;ContentIdentity.id&gt;</t>
-  </si>
-  <si>
-    <t>i32</t>
-  </si>
-  <si>
-    <t>enum&lt;CombatPath&gt;</t>
-  </si>
-  <si>
-    <t>enum&lt;LightConeApplicability&gt;</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>range=3..5</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -128,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -422,136 +407,552 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>LightCone</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>9de39463d2f7c2f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>rarity</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>path</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>applicability</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>passive_rule_identity_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>rarity</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>path</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>applicability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>passive_rule_identity_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ref&lt;ContentIdentity.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>enum&lt;CombatPath&gt;</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>enum&lt;LightConeApplicability&gt;</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ref&lt;ContentIdentity.id&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>range=3..5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>112</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>210001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>113</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>210002</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>114</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>210003</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>115</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>210004</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>116</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>210005</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>117</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>210006</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>118</v>
+      </c>
+      <c r="C14" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>210007</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>119</v>
+      </c>
+      <c r="C15" t="n">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>210008</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>120</v>
+      </c>
+      <c r="C16" t="n">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>210009</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>121</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>210010</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>122</v>
+      </c>
+      <c r="C18" t="n">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>210011</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>123</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>210012</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>124</v>
+      </c>
+      <c r="C20" t="n">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>25</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>210013</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>125</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>210014</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>126</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>210015</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>127</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>210016</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/LightCone.xlsx
+++ b/config/data/LightCone.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -955,6 +955,342 @@
         <v>210016</v>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>128</v>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>220001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>129</v>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>220002</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>130</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>220003</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>131</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>220004</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>132</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>220005</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>133</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>220006</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>134</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Abundance</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>220007</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>135</v>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>220008</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>136</v>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>220009</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>137</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>220010</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>138</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>220011</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>139</v>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>220012</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>140</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>220013</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>141</v>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Elation</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>220014</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>142</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>220015</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>143</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>220016</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/LightCone.xlsx
+++ b/config/data/LightCone.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,6 +1291,342 @@
         <v>220016</v>
       </c>
     </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>144</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Abundance</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>230001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>145</v>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>230002</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>146</v>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>230003</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>147</v>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Abundance</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>230004</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>148</v>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Elation</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>230005</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>149</v>
+      </c>
+      <c r="C45" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>230006</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>150</v>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>230007</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>151</v>
+      </c>
+      <c r="C47" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>230008</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>152</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>230009</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>153</v>
+      </c>
+      <c r="C49" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>230010</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>154</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Abundance</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>230011</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>155</v>
+      </c>
+      <c r="C51" t="n">
+        <v>5</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>230012</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>156</v>
+      </c>
+      <c r="C52" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>230013</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>157</v>
+      </c>
+      <c r="C53" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>230014</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>158</v>
+      </c>
+      <c r="C54" t="n">
+        <v>5</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>230015</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>159</v>
+      </c>
+      <c r="C55" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Remembrance</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>230016</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/LightCone.xlsx
+++ b/config/data/LightCone.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1627,6 +1627,342 @@
         <v>230016</v>
       </c>
     </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>160</v>
+      </c>
+      <c r="C56" t="n">
+        <v>4</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>240001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>161</v>
+      </c>
+      <c r="C57" t="n">
+        <v>4</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Remembrance</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>240002</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>162</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>240003</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>163</v>
+      </c>
+      <c r="C59" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>240004</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>164</v>
+      </c>
+      <c r="C60" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Abundance</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>240005</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>165</v>
+      </c>
+      <c r="C61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>240006</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>166</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>240007</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>167</v>
+      </c>
+      <c r="C63" t="n">
+        <v>5</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>240008</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>168</v>
+      </c>
+      <c r="C64" t="n">
+        <v>5</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>240009</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>169</v>
+      </c>
+      <c r="C65" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>240010</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>170</v>
+      </c>
+      <c r="C66" t="n">
+        <v>5</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>240011</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>171</v>
+      </c>
+      <c r="C67" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>240012</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>172</v>
+      </c>
+      <c r="C68" t="n">
+        <v>5</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>240013</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>173</v>
+      </c>
+      <c r="C69" t="n">
+        <v>5</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>240014</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>174</v>
+      </c>
+      <c r="C70" t="n">
+        <v>5</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>240015</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>175</v>
+      </c>
+      <c r="C71" t="n">
+        <v>4</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>240016</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/LightCone.xlsx
+++ b/config/data/LightCone.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1963,6 +1963,342 @@
         <v>240016</v>
       </c>
     </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>176</v>
+      </c>
+      <c r="C72" t="n">
+        <v>5</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>250001</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>177</v>
+      </c>
+      <c r="C73" t="n">
+        <v>5</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>250002</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>178</v>
+      </c>
+      <c r="C74" t="n">
+        <v>4</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>250003</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>179</v>
+      </c>
+      <c r="C75" t="n">
+        <v>4</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>250004</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>180</v>
+      </c>
+      <c r="C76" t="n">
+        <v>4</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>250005</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>181</v>
+      </c>
+      <c r="C77" t="n">
+        <v>5</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>250006</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>182</v>
+      </c>
+      <c r="C78" t="n">
+        <v>5</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>250007</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>183</v>
+      </c>
+      <c r="C79" t="n">
+        <v>3</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Elation</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>250008</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>184</v>
+      </c>
+      <c r="C80" t="n">
+        <v>5</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Remembrance</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>250009</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>185</v>
+      </c>
+      <c r="C81" t="n">
+        <v>5</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>250010</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>186</v>
+      </c>
+      <c r="C82" t="n">
+        <v>3</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>250011</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>187</v>
+      </c>
+      <c r="C83" t="n">
+        <v>5</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Remembrance</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>250012</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>188</v>
+      </c>
+      <c r="C84" t="n">
+        <v>4</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>250013</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>189</v>
+      </c>
+      <c r="C85" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>250014</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>190</v>
+      </c>
+      <c r="C86" t="n">
+        <v>4</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>250015</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>191</v>
+      </c>
+      <c r="C87" t="n">
+        <v>5</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Remembrance</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>250016</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/LightCone.xlsx
+++ b/config/data/LightCone.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2299,6 +2299,342 @@
         <v>250016</v>
       </c>
     </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>192</v>
+      </c>
+      <c r="C88" t="n">
+        <v>3</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>260001</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>193</v>
+      </c>
+      <c r="C89" t="n">
+        <v>5</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>260002</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>194</v>
+      </c>
+      <c r="C90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Abundance</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>260003</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>195</v>
+      </c>
+      <c r="C91" t="n">
+        <v>4</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Elation</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>260004</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>196</v>
+      </c>
+      <c r="C92" t="n">
+        <v>3</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>260005</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>197</v>
+      </c>
+      <c r="C93" t="n">
+        <v>5</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>260006</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>198</v>
+      </c>
+      <c r="C94" t="n">
+        <v>5</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Abundance</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>260007</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>199</v>
+      </c>
+      <c r="C95" t="n">
+        <v>5</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>260008</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>200</v>
+      </c>
+      <c r="C96" t="n">
+        <v>4</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>260009</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>201</v>
+      </c>
+      <c r="C97" t="n">
+        <v>5</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>260010</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>202</v>
+      </c>
+      <c r="C98" t="n">
+        <v>4</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>260011</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>203</v>
+      </c>
+      <c r="C99" t="n">
+        <v>5</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>260012</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>204</v>
+      </c>
+      <c r="C100" t="n">
+        <v>4</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>260013</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>205</v>
+      </c>
+      <c r="C101" t="n">
+        <v>3</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>260014</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>206</v>
+      </c>
+      <c r="C102" t="n">
+        <v>4</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>260015</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>207</v>
+      </c>
+      <c r="C103" t="n">
+        <v>5</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>260016</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/LightCone.xlsx
+++ b/config/data/LightCone.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2635,6 +2635,342 @@
         <v>260016</v>
       </c>
     </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>208</v>
+      </c>
+      <c r="C104" t="n">
+        <v>5</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>270001</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>209</v>
+      </c>
+      <c r="C105" t="n">
+        <v>4</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Abundance</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>270002</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>210</v>
+      </c>
+      <c r="C106" t="n">
+        <v>3</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>270003</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>211</v>
+      </c>
+      <c r="C107" t="n">
+        <v>4</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>270004</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>212</v>
+      </c>
+      <c r="C108" t="n">
+        <v>4</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>270005</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>213</v>
+      </c>
+      <c r="C109" t="n">
+        <v>4</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Abundance</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>270006</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>214</v>
+      </c>
+      <c r="C110" t="n">
+        <v>4</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Abundance</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>270007</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>215</v>
+      </c>
+      <c r="C111" t="n">
+        <v>5</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>270008</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>216</v>
+      </c>
+      <c r="C112" t="n">
+        <v>5</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>270009</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>217</v>
+      </c>
+      <c r="C113" t="n">
+        <v>3</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Remembrance</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>270010</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>218</v>
+      </c>
+      <c r="C114" t="n">
+        <v>4</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>270011</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>219</v>
+      </c>
+      <c r="C115" t="n">
+        <v>4</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>270012</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>220</v>
+      </c>
+      <c r="C116" t="n">
+        <v>4</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>270013</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>221</v>
+      </c>
+      <c r="C117" t="n">
+        <v>3</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>270014</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>222</v>
+      </c>
+      <c r="C118" t="n">
+        <v>5</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>270015</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>223</v>
+      </c>
+      <c r="C119" t="n">
+        <v>5</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Abundance</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>270016</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/LightCone.xlsx
+++ b/config/data/LightCone.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2971,6 +2971,342 @@
         <v>270016</v>
       </c>
     </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>224</v>
+      </c>
+      <c r="C120" t="n">
+        <v>4</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>280001</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>225</v>
+      </c>
+      <c r="C121" t="n">
+        <v>3</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Remembrance</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>280002</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>226</v>
+      </c>
+      <c r="C122" t="n">
+        <v>4</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>280003</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>227</v>
+      </c>
+      <c r="C123" t="n">
+        <v>4</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Abundance</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>280004</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>228</v>
+      </c>
+      <c r="C124" t="n">
+        <v>3</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>280005</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>229</v>
+      </c>
+      <c r="C125" t="n">
+        <v>5</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>280006</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>230</v>
+      </c>
+      <c r="C126" t="n">
+        <v>5</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>280007</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>231</v>
+      </c>
+      <c r="C127" t="n">
+        <v>3</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Elation</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>280008</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>232</v>
+      </c>
+      <c r="C128" t="n">
+        <v>5</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>280009</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>233</v>
+      </c>
+      <c r="C129" t="n">
+        <v>5</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>280010</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>234</v>
+      </c>
+      <c r="C130" t="n">
+        <v>4</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>280011</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>235</v>
+      </c>
+      <c r="C131" t="n">
+        <v>4</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Remembrance</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>280012</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>236</v>
+      </c>
+      <c r="C132" t="n">
+        <v>4</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>280013</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>237</v>
+      </c>
+      <c r="C133" t="n">
+        <v>5</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>280014</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>238</v>
+      </c>
+      <c r="C134" t="n">
+        <v>4</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>280015</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>239</v>
+      </c>
+      <c r="C135" t="n">
+        <v>4</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>280016</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/LightCone.xlsx
+++ b/config/data/LightCone.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J135"/>
+  <dimension ref="A1:J151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3307,6 +3307,342 @@
         <v>280016</v>
       </c>
     </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>240</v>
+      </c>
+      <c r="C136" t="n">
+        <v>5</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>290001</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>241</v>
+      </c>
+      <c r="C137" t="n">
+        <v>4</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Remembrance</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>290002</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>242</v>
+      </c>
+      <c r="C138" t="n">
+        <v>4</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Harmony</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>290003</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>243</v>
+      </c>
+      <c r="C139" t="n">
+        <v>4</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>290004</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>244</v>
+      </c>
+      <c r="C140" t="n">
+        <v>5</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>290005</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>245</v>
+      </c>
+      <c r="C141" t="n">
+        <v>4</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>290006</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>246</v>
+      </c>
+      <c r="C142" t="n">
+        <v>4</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>290007</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>247</v>
+      </c>
+      <c r="C143" t="n">
+        <v>4</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Remembrance</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>290008</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>248</v>
+      </c>
+      <c r="C144" t="n">
+        <v>5</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>290009</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>249</v>
+      </c>
+      <c r="C145" t="n">
+        <v>4</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>290010</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>250</v>
+      </c>
+      <c r="C146" t="n">
+        <v>5</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Remembrance</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>290011</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>251</v>
+      </c>
+      <c r="C147" t="n">
+        <v>5</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>290012</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>252</v>
+      </c>
+      <c r="C148" t="n">
+        <v>5</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>290013</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>253</v>
+      </c>
+      <c r="C149" t="n">
+        <v>5</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>290014</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>254</v>
+      </c>
+      <c r="C150" t="n">
+        <v>5</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Abundance</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>290015</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>255</v>
+      </c>
+      <c r="C151" t="n">
+        <v>5</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Remembrance</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>290016</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/LightCone.xlsx
+++ b/config/data/LightCone.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J151"/>
+  <dimension ref="A1:J167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3643,6 +3643,342 @@
         <v>290016</v>
       </c>
     </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>256</v>
+      </c>
+      <c r="C152" t="n">
+        <v>5</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Remembrance</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>300001</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>257</v>
+      </c>
+      <c r="C153" t="n">
+        <v>4</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>300002</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>258</v>
+      </c>
+      <c r="C154" t="n">
+        <v>4</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Elation</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>300003</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>259</v>
+      </c>
+      <c r="C155" t="n">
+        <v>4</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Elation</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>300004</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>260</v>
+      </c>
+      <c r="C156" t="n">
+        <v>4</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>300005</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>261</v>
+      </c>
+      <c r="C157" t="n">
+        <v>4</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>300006</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>262</v>
+      </c>
+      <c r="C158" t="n">
+        <v>5</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Elation</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>300007</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>263</v>
+      </c>
+      <c r="C159" t="n">
+        <v>4</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Abundance</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>300008</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>264</v>
+      </c>
+      <c r="C160" t="n">
+        <v>4</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Remembrance</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>300009</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>265</v>
+      </c>
+      <c r="C161" t="n">
+        <v>3</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>300010</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>266</v>
+      </c>
+      <c r="C162" t="n">
+        <v>4</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Abundance</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>300011</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>267</v>
+      </c>
+      <c r="C163" t="n">
+        <v>4</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>300012</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>268</v>
+      </c>
+      <c r="C164" t="n">
+        <v>4</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>300013</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>269</v>
+      </c>
+      <c r="C165" t="n">
+        <v>5</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Elation</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>300014</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>270</v>
+      </c>
+      <c r="C166" t="n">
+        <v>4</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Abundance</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>300015</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>271</v>
+      </c>
+      <c r="C167" t="n">
+        <v>5</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Elation</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>300016</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/LightCone.xlsx
+++ b/config/data/LightCone.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J167"/>
+  <dimension ref="A1:J172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3979,6 +3979,111 @@
         <v>300016</v>
       </c>
     </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>272</v>
+      </c>
+      <c r="C168" t="n">
+        <v>5</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>310001</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>273</v>
+      </c>
+      <c r="C169" t="n">
+        <v>5</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Nihility</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>310002</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>274</v>
+      </c>
+      <c r="C170" t="n">
+        <v>4</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Destruction</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>310003</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>275</v>
+      </c>
+      <c r="C171" t="n">
+        <v>5</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>310004</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>276</v>
+      </c>
+      <c r="C172" t="n">
+        <v>5</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>310005</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/LightCone.xlsx
+++ b/config/data/LightCone.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="LightCone" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LightCone" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -24,16 +24,68 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F2937"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3A4A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9EEF5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3D6E8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE5EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -41,12 +93,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,3677 +499,5221 @@
   </sheetPr>
   <dimension ref="A1:J172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.7109375" customWidth="1" min="1" max="1"/>
+    <col width="23.7109375" customWidth="1" style="5" min="2" max="2"/>
+    <col width="19.7109375" customWidth="1" style="5" min="3" max="3"/>
+    <col width="12.7109375" customWidth="1" style="5" min="4" max="4"/>
+    <col width="16.7109375" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28.7109375" customWidth="1" style="5" min="6" max="6"/>
+    <col width="24.7109375" customWidth="1" style="5" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>@table</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>LightCone</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>@mode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>@key</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>@scope</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>@schema</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>9de39463d2f7c2f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>d760289c16db864c</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>#name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>source_equipment_id</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>rarity</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>applicability</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>passive_rule_identity_id</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>#field</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>source_equipment_id</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>rarity</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>applicability</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>passive_rule_identity_id</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>#type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>ref&lt;ContentIdentity.id&gt;</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>i32</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>enum&lt;CombatPath&gt;</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>enum&lt;LightConeApplicability&gt;</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>ref&lt;ContentIdentity.id&gt;</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>#scope</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>all</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>#input</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>range=3..5</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>#desc</t>
         </is>
       </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" t="n">
-        <v>112</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>21060</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>210001</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>210001</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
-        <v>113</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>23034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>210002</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>210002</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
-        <v>114</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>21012</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>210003</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>210003</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
-        <v>115</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>23060</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>210004</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>210004</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
-        <v>116</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>23045</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>210005</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>210005</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
-        <v>117</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>21058</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>210006</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>210006</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
-        <v>118</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>20014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>210007</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>210007</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
-        <v>119</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>21045</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>210008</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>210008</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
-        <v>120</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>23024</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>210009</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>210009</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
-        <v>121</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>20003</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>Preservation</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>210010</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>210010</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
-        <v>122</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>23018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>210011</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>210011</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
-        <v>123</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>20000</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>210012</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>210012</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
-        <v>124</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>23020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>210013</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>210013</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
-        <v>125</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>23010</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>210014</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>210014</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
-        <v>126</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>22000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>210015</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>210015</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
-        <v>127</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>21044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>210016</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>210016</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
-        <v>128</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>23015</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>220001</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>220001</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
-        <v>129</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>23003</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>220002</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>220002</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="n">
-        <v>130</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>21032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>220003</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>220003</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="n">
-        <v>131</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>20005</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>220004</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>220004</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="n">
-        <v>132</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>20002</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>220005</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>220005</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="n">
-        <v>133</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>21043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>Preservation</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>220006</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>220006</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="n">
-        <v>134</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>20001</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>Abundance</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>220007</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>220007</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="n">
-        <v>135</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>24001</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>220008</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>220008</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="n">
-        <v>136</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>23030</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>220009</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>220009</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="n">
-        <v>137</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>21018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>220010</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>220010</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="n">
-        <v>138</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>20007</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>220011</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>220011</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="n">
-        <v>139</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>20006</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>220012</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>220012</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="n">
-        <v>140</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>21002</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Preservation</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>220013</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>220013</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="n">
-        <v>141</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>23053</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>Elation</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>220014</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>220014</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="n">
-        <v>142</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>20010</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>Preservation</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>220015</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>220015</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="n">
-        <v>143</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>21039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>Preservation</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>220016</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>220016</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="n">
-        <v>144</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>21048</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>Abundance</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>230001</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>230001</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="n">
-        <v>145</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>21036</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>230002</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>230002</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="n">
-        <v>146</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>23021</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>230003</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>230003</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="n">
-        <v>147</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>23008</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>Abundance</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>230004</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>230004</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="n">
-        <v>148</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>24006</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>Elation</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>230005</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>230005</t>
+        </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="n">
-        <v>149</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>23048</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>230006</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>230006</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="n">
-        <v>150</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>24004</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>230007</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>230007</t>
+        </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="n">
-        <v>151</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>21008</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>230008</v>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>230008</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="n">
-        <v>152</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>21022</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>230009</v>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>230009</t>
+        </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="n">
-        <v>153</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>21037</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>230010</v>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>230010</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="n">
-        <v>154</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>20008</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>Abundance</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>230011</v>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>230011</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="n">
-        <v>155</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>23039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>230012</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>230012</t>
+        </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="n">
-        <v>156</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>21038</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>230013</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>230013</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="n">
-        <v>157</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>23061</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>230014</v>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>230014</t>
+        </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="n">
-        <v>158</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>23026</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>230015</v>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>230015</t>
+        </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="n">
-        <v>159</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>22006</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>Remembrance</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>230016</v>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>230016</t>
+        </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="n">
-        <v>160</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>22002</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>240001</v>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>240001</t>
+        </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="n">
-        <v>161</v>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>21051</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>Remembrance</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>240002</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>240002</t>
+        </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="n">
-        <v>162</v>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>21020</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>240003</v>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>240003</t>
+        </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="n">
-        <v>163</v>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>21001</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>240004</v>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>240004</t>
+        </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="n">
-        <v>164</v>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>22001</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>Abundance</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>240005</v>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>240005</t>
+        </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="n">
-        <v>165</v>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>20018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>240006</v>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>240006</t>
+        </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="n">
-        <v>166</v>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>21061</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>240007</v>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>240007</t>
+        </is>
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="n">
-        <v>167</v>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
       </c>
       <c r="C63" t="n">
-        <v>5</v>
+        <v>23062</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>240008</v>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>240008</t>
+        </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="n">
-        <v>168</v>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>23014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>240009</v>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>240009</t>
+        </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="n">
-        <v>169</v>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>23031</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>240010</v>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>240010</t>
+        </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="n">
-        <v>170</v>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>23038</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>240011</v>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>240011</t>
+        </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="n">
-        <v>171</v>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>21056</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>240012</v>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>240012</t>
+        </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="n">
-        <v>172</v>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>23004</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>240013</v>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>240013</t>
+        </is>
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="n">
-        <v>173</v>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>23001</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>240014</v>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>240014</t>
+        </is>
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="n">
-        <v>174</v>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>23007</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>240015</v>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>240015</t>
+        </is>
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="n">
-        <v>175</v>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>21042</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>240016</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>240016</t>
+        </is>
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="n">
-        <v>176</v>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>23023</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>Preservation</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>250001</v>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>250001</t>
+        </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="n">
-        <v>177</v>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>23037</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>250002</v>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>250002</t>
+        </is>
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="n">
-        <v>178</v>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>21041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>250003</v>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>250003</t>
+        </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="n">
-        <v>179</v>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>21053</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>Preservation</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>250004</v>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>250004</t>
+        </is>
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="n">
-        <v>180</v>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>21009</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>Preservation</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>250005</v>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>250005</t>
+        </is>
       </c>
     </row>
     <row r="77">
-      <c r="B77" t="n">
-        <v>181</v>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>23043</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>250006</v>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>250006</t>
+        </is>
       </c>
     </row>
     <row r="78">
-      <c r="B78" t="n">
-        <v>182</v>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
       </c>
       <c r="C78" t="n">
-        <v>5</v>
+        <v>23041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>250007</v>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>250007</t>
+        </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" t="n">
-        <v>183</v>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>20024</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>Elation</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>250008</v>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>250008</t>
+        </is>
       </c>
     </row>
     <row r="80">
-      <c r="B80" t="n">
-        <v>184</v>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>23042</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>Remembrance</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>250009</v>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>250009</t>
+        </is>
       </c>
     </row>
     <row r="81">
-      <c r="B81" t="n">
-        <v>185</v>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>23035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>250010</v>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>250010</t>
+        </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" t="n">
-        <v>186</v>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>20011</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>250011</v>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>250011</t>
+        </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" t="n">
-        <v>187</v>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>23040</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>Remembrance</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>250012</v>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>250012</t>
+        </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" t="n">
-        <v>188</v>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>21013</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>250013</v>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>250013</t>
+        </is>
       </c>
     </row>
     <row r="85">
-      <c r="B85" t="n">
-        <v>189</v>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>20019</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>250014</v>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>250014</t>
+        </is>
       </c>
     </row>
     <row r="86">
-      <c r="B86" t="n">
-        <v>190</v>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>21004</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>250015</v>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>250015</t>
+        </is>
       </c>
     </row>
     <row r="87">
-      <c r="B87" t="n">
-        <v>191</v>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
+        <v>24005</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>Remembrance</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>250016</v>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>250016</t>
+        </is>
       </c>
     </row>
     <row r="88">
-      <c r="B88" t="n">
-        <v>192</v>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>20012</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>260001</v>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>260001</t>
+        </is>
       </c>
     </row>
     <row r="89">
-      <c r="B89" t="n">
-        <v>193</v>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>23005</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>Preservation</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>260002</v>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>260002</t>
+        </is>
       </c>
     </row>
     <row r="90">
-      <c r="B90" t="n">
-        <v>194</v>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>20015</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>Abundance</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>260003</v>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>260003</t>
+        </is>
       </c>
     </row>
     <row r="91">
-      <c r="B91" t="n">
-        <v>195</v>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>21064</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>Elation</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>260004</v>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>260004</t>
+        </is>
       </c>
     </row>
     <row r="92">
-      <c r="B92" t="n">
-        <v>196</v>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>20016</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>260005</v>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>260005</t>
+        </is>
       </c>
     </row>
     <row r="93">
-      <c r="B93" t="n">
-        <v>197</v>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>23050</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>260006</v>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>260006</t>
+        </is>
       </c>
     </row>
     <row r="94">
-      <c r="B94" t="n">
-        <v>198</v>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>23017</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>Abundance</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>260007</v>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>260007</t>
+        </is>
       </c>
     </row>
     <row r="95">
-      <c r="B95" t="n">
-        <v>199</v>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>23000</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>260008</v>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>260008</t>
+        </is>
       </c>
     </row>
     <row r="96">
-      <c r="B96" t="n">
-        <v>200</v>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>22003</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>260009</v>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>260009</t>
+        </is>
       </c>
     </row>
     <row r="97">
-      <c r="B97" t="n">
-        <v>201</v>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>23033</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>260010</v>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>260010</t>
+        </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" t="n">
-        <v>202</v>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>21033</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>260011</v>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>260011</t>
+        </is>
       </c>
     </row>
     <row r="99">
-      <c r="B99" t="n">
-        <v>203</v>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
       </c>
       <c r="C99" t="n">
-        <v>5</v>
+        <v>24000</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>260012</v>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>260012</t>
+        </is>
       </c>
     </row>
     <row r="100">
-      <c r="B100" t="n">
-        <v>204</v>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>21003</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>260013</v>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>260013</t>
+        </is>
       </c>
     </row>
     <row r="101">
-      <c r="B101" t="n">
-        <v>205</v>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>20013</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>260014</v>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>260014</t>
+        </is>
       </c>
     </row>
     <row r="102">
-      <c r="B102" t="n">
-        <v>206</v>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>21025</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F102" t="n">
-        <v>260015</v>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>260015</t>
+        </is>
       </c>
     </row>
     <row r="103">
-      <c r="B103" t="n">
-        <v>207</v>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
       </c>
       <c r="C103" t="n">
-        <v>5</v>
+        <v>23019</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F103" t="n">
-        <v>260016</v>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>260016</t>
+        </is>
       </c>
     </row>
     <row r="104">
-      <c r="B104" t="n">
-        <v>208</v>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
       </c>
       <c r="C104" t="n">
-        <v>5</v>
+        <v>23006</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F104" t="n">
-        <v>270001</v>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>270001</t>
+        </is>
       </c>
     </row>
     <row r="105">
-      <c r="B105" t="n">
-        <v>209</v>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>21014</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>Abundance</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F105" t="n">
-        <v>270002</v>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>270002</t>
+        </is>
       </c>
     </row>
     <row r="106">
-      <c r="B106" t="n">
-        <v>210</v>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>20017</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
           <t>Preservation</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F106" t="n">
-        <v>270003</v>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>270003</t>
+        </is>
       </c>
     </row>
     <row r="107">
-      <c r="B107" t="n">
-        <v>211</v>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>21011</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F107" t="n">
-        <v>270004</v>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>270004</t>
+        </is>
       </c>
     </row>
     <row r="108">
-      <c r="B108" t="n">
-        <v>212</v>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
       </c>
       <c r="C108" t="n">
-        <v>4</v>
+        <v>21046</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
-        <v>270005</v>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>270005</t>
+        </is>
       </c>
     </row>
     <row r="109">
-      <c r="B109" t="n">
-        <v>213</v>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
       </c>
       <c r="C109" t="n">
-        <v>4</v>
+        <v>21000</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
           <t>Abundance</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F109" t="n">
-        <v>270006</v>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>270006</t>
+        </is>
       </c>
     </row>
     <row r="110">
-      <c r="B110" t="n">
-        <v>214</v>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
       </c>
       <c r="C110" t="n">
-        <v>4</v>
+        <v>21021</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>Abundance</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F110" t="n">
-        <v>270007</v>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>270007</t>
+        </is>
       </c>
     </row>
     <row r="111">
-      <c r="B111" t="n">
-        <v>215</v>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
       </c>
       <c r="C111" t="n">
-        <v>5</v>
+        <v>23059</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F111" t="n">
-        <v>270008</v>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>270008</t>
+        </is>
       </c>
     </row>
     <row r="112">
-      <c r="B112" t="n">
-        <v>216</v>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
       </c>
       <c r="C112" t="n">
-        <v>5</v>
+        <v>23022</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F112" t="n">
-        <v>270009</v>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>270009</t>
+        </is>
       </c>
     </row>
     <row r="113">
-      <c r="B113" t="n">
-        <v>217</v>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>20022</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
           <t>Remembrance</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F113" t="n">
-        <v>270010</v>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>270010</t>
+        </is>
       </c>
     </row>
     <row r="114">
-      <c r="B114" t="n">
-        <v>218</v>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
       </c>
       <c r="C114" t="n">
-        <v>4</v>
+        <v>21015</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F114" t="n">
-        <v>270011</v>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>270011</t>
+        </is>
       </c>
     </row>
     <row r="115">
-      <c r="B115" t="n">
-        <v>219</v>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
       </c>
       <c r="C115" t="n">
-        <v>4</v>
+        <v>21031</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F115" t="n">
-        <v>270012</v>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>270012</t>
+        </is>
       </c>
     </row>
     <row r="116">
-      <c r="B116" t="n">
-        <v>220</v>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
       </c>
       <c r="C116" t="n">
-        <v>4</v>
+        <v>21024</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
-        <v>270013</v>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>270013</t>
+        </is>
       </c>
     </row>
     <row r="117">
-      <c r="B117" t="n">
-        <v>221</v>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
       </c>
       <c r="C117" t="n">
-        <v>3</v>
+        <v>20020</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F117" t="n">
-        <v>270014</v>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>270014</t>
+        </is>
       </c>
     </row>
     <row r="118">
-      <c r="B118" t="n">
-        <v>222</v>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
       </c>
       <c r="C118" t="n">
-        <v>5</v>
+        <v>23027</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F118" t="n">
-        <v>270015</v>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>270015</t>
+        </is>
       </c>
     </row>
     <row r="119">
-      <c r="B119" t="n">
-        <v>223</v>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
       </c>
       <c r="C119" t="n">
-        <v>5</v>
+        <v>23032</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
           <t>Abundance</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
-        <v>270016</v>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>270016</t>
+        </is>
       </c>
     </row>
     <row r="120">
-      <c r="B120" t="n">
-        <v>224</v>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
       </c>
       <c r="C120" t="n">
-        <v>4</v>
+        <v>21062</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>280001</v>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>280001</t>
+        </is>
       </c>
     </row>
     <row r="121">
-      <c r="B121" t="n">
-        <v>225</v>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>20021</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
           <t>Remembrance</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
-        <v>280002</v>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>280002</t>
+        </is>
       </c>
     </row>
     <row r="122">
-      <c r="B122" t="n">
-        <v>226</v>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
       </c>
       <c r="C122" t="n">
-        <v>4</v>
+        <v>21047</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F122" t="n">
-        <v>280003</v>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>280003</t>
+        </is>
       </c>
     </row>
     <row r="123">
-      <c r="B123" t="n">
-        <v>227</v>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
       </c>
       <c r="C123" t="n">
-        <v>4</v>
+        <v>21007</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
           <t>Abundance</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F123" t="n">
-        <v>280004</v>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>280004</t>
+        </is>
       </c>
     </row>
     <row r="124">
-      <c r="B124" t="n">
-        <v>228</v>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
+        <v>20009</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F124" t="n">
-        <v>280005</v>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>280005</t>
+        </is>
       </c>
     </row>
     <row r="125">
-      <c r="B125" t="n">
-        <v>229</v>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
       </c>
       <c r="C125" t="n">
-        <v>5</v>
+        <v>23011</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
           <t>Preservation</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>280006</v>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>280006</t>
+        </is>
       </c>
     </row>
     <row r="126">
-      <c r="B126" t="n">
-        <v>230</v>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
       </c>
       <c r="C126" t="n">
-        <v>5</v>
+        <v>23012</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F126" t="n">
-        <v>280007</v>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>280007</t>
+        </is>
       </c>
     </row>
     <row r="127">
-      <c r="B127" t="n">
-        <v>231</v>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>20023</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
           <t>Elation</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F127" t="n">
-        <v>280008</v>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>280008</t>
+        </is>
       </c>
     </row>
     <row r="128">
-      <c r="B128" t="n">
-        <v>232</v>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
       </c>
       <c r="C128" t="n">
-        <v>5</v>
+        <v>24003</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F128" t="n">
-        <v>280009</v>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>280009</t>
+        </is>
       </c>
     </row>
     <row r="129">
-      <c r="B129" t="n">
-        <v>233</v>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
       </c>
       <c r="C129" t="n">
-        <v>5</v>
+        <v>23002</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
-        <v>280010</v>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>280010</t>
+        </is>
       </c>
     </row>
     <row r="130">
-      <c r="B130" t="n">
-        <v>234</v>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
       </c>
       <c r="C130" t="n">
-        <v>4</v>
+        <v>21017</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F130" t="n">
-        <v>280011</v>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>280011</t>
+        </is>
       </c>
     </row>
     <row r="131">
-      <c r="B131" t="n">
-        <v>235</v>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
       </c>
       <c r="C131" t="n">
-        <v>4</v>
+        <v>21052</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
           <t>Remembrance</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F131" t="n">
-        <v>280012</v>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>280012</t>
+        </is>
       </c>
     </row>
     <row r="132">
-      <c r="B132" t="n">
-        <v>236</v>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
       </c>
       <c r="C132" t="n">
-        <v>4</v>
+        <v>21010</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F132" t="n">
-        <v>280013</v>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>280013</t>
+        </is>
       </c>
     </row>
     <row r="133">
-      <c r="B133" t="n">
-        <v>237</v>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
       </c>
       <c r="C133" t="n">
-        <v>5</v>
+        <v>24002</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
           <t>Preservation</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F133" t="n">
-        <v>280014</v>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>280014</t>
+        </is>
       </c>
     </row>
     <row r="134">
-      <c r="B134" t="n">
-        <v>238</v>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
       </c>
       <c r="C134" t="n">
-        <v>4</v>
+        <v>21006</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F134" t="n">
-        <v>280015</v>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>280015</t>
+        </is>
       </c>
     </row>
     <row r="135">
-      <c r="B135" t="n">
-        <v>239</v>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
       </c>
       <c r="C135" t="n">
-        <v>4</v>
+        <v>21040</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F135" t="n">
-        <v>280016</v>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>280016</t>
+        </is>
       </c>
     </row>
     <row r="136">
-      <c r="B136" t="n">
-        <v>240</v>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
       </c>
       <c r="C136" t="n">
-        <v>5</v>
+        <v>23056</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F136" t="n">
-        <v>290001</v>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>290001</t>
+        </is>
       </c>
     </row>
     <row r="137">
-      <c r="B137" t="n">
-        <v>241</v>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
       </c>
       <c r="C137" t="n">
-        <v>4</v>
+        <v>21057</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
           <t>Remembrance</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F137" t="n">
-        <v>290002</v>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>290002</t>
+        </is>
       </c>
     </row>
     <row r="138">
-      <c r="B138" t="n">
-        <v>242</v>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
       </c>
       <c r="C138" t="n">
-        <v>4</v>
+        <v>22005</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
           <t>Harmony</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F138" t="n">
-        <v>290003</v>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>290003</t>
+        </is>
       </c>
     </row>
     <row r="139">
-      <c r="B139" t="n">
-        <v>243</v>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
       </c>
       <c r="C139" t="n">
-        <v>4</v>
+        <v>22004</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F139" t="n">
-        <v>290004</v>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>290004</t>
+        </is>
       </c>
     </row>
     <row r="140">
-      <c r="B140" t="n">
-        <v>244</v>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
       </c>
       <c r="C140" t="n">
-        <v>5</v>
+        <v>23046</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F140" t="n">
-        <v>290005</v>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>290005</t>
+        </is>
       </c>
     </row>
     <row r="141">
-      <c r="B141" t="n">
-        <v>245</v>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
       </c>
       <c r="C141" t="n">
-        <v>4</v>
+        <v>21005</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F141" t="n">
-        <v>290006</v>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>290006</t>
+        </is>
       </c>
     </row>
     <row r="142">
-      <c r="B142" t="n">
-        <v>246</v>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
       </c>
       <c r="C142" t="n">
-        <v>4</v>
+        <v>21027</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F142" t="n">
-        <v>290007</v>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>290007</t>
+        </is>
       </c>
     </row>
     <row r="143">
-      <c r="B143" t="n">
-        <v>247</v>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
       </c>
       <c r="C143" t="n">
-        <v>4</v>
+        <v>21054</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
           <t>Remembrance</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F143" t="n">
-        <v>290008</v>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>290008</t>
+        </is>
       </c>
     </row>
     <row r="144">
-      <c r="B144" t="n">
-        <v>248</v>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
       </c>
       <c r="C144" t="n">
-        <v>5</v>
+        <v>23009</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F144" t="n">
-        <v>290009</v>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>290009</t>
+        </is>
       </c>
     </row>
     <row r="145">
-      <c r="B145" t="n">
-        <v>249</v>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
       </c>
       <c r="C145" t="n">
-        <v>4</v>
+        <v>21030</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
           <t>Preservation</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F145" t="n">
-        <v>290010</v>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>290010</t>
+        </is>
       </c>
     </row>
     <row r="146">
-      <c r="B146" t="n">
-        <v>250</v>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="C146" t="n">
-        <v>5</v>
+        <v>23052</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
           <t>Remembrance</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F146" t="n">
-        <v>290011</v>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>290011</t>
+        </is>
       </c>
     </row>
     <row r="147">
-      <c r="B147" t="n">
-        <v>251</v>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
       </c>
       <c r="C147" t="n">
-        <v>5</v>
+        <v>23029</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F147" t="n">
-        <v>290012</v>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>290012</t>
+        </is>
       </c>
     </row>
     <row r="148">
-      <c r="B148" t="n">
-        <v>252</v>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
       </c>
       <c r="C148" t="n">
-        <v>5</v>
+        <v>23051</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
           <t>Preservation</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F148" t="n">
-        <v>290013</v>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>290013</t>
+        </is>
       </c>
     </row>
     <row r="149">
-      <c r="B149" t="n">
-        <v>253</v>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
       </c>
       <c r="C149" t="n">
-        <v>5</v>
+        <v>23044</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F149" t="n">
-        <v>290014</v>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>290014</t>
+        </is>
       </c>
     </row>
     <row r="150">
-      <c r="B150" t="n">
-        <v>254</v>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
       </c>
       <c r="C150" t="n">
-        <v>5</v>
+        <v>23013</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
           <t>Abundance</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F150" t="n">
-        <v>290015</v>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>290015</t>
+        </is>
       </c>
     </row>
     <row r="151">
-      <c r="B151" t="n">
-        <v>255</v>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
       </c>
       <c r="C151" t="n">
-        <v>5</v>
+        <v>23036</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
           <t>Remembrance</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F151" t="n">
-        <v>290016</v>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>290016</t>
+        </is>
       </c>
     </row>
     <row r="152">
-      <c r="B152" t="n">
-        <v>256</v>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
       </c>
       <c r="C152" t="n">
-        <v>5</v>
+        <v>23049</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
           <t>Remembrance</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F152" t="n">
-        <v>300001</v>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>300001</t>
+        </is>
       </c>
     </row>
     <row r="153">
-      <c r="B153" t="n">
-        <v>257</v>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
       </c>
       <c r="C153" t="n">
-        <v>4</v>
+        <v>21034</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F153" t="n">
-        <v>300002</v>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>300002</t>
+        </is>
       </c>
     </row>
     <row r="154">
-      <c r="B154" t="n">
-        <v>258</v>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
       </c>
       <c r="C154" t="n">
-        <v>4</v>
+        <v>21065</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
           <t>Elation</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F154" t="n">
-        <v>300003</v>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>300003</t>
+        </is>
       </c>
     </row>
     <row r="155">
-      <c r="B155" t="n">
-        <v>259</v>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
       </c>
       <c r="C155" t="n">
-        <v>4</v>
+        <v>22007</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
           <t>Elation</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F155" t="n">
-        <v>300004</v>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>300004</t>
+        </is>
       </c>
     </row>
     <row r="156">
-      <c r="B156" t="n">
-        <v>260</v>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
       </c>
       <c r="C156" t="n">
-        <v>4</v>
+        <v>21016</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
           <t>Preservation</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F156" t="n">
-        <v>300005</v>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>300005</t>
+        </is>
       </c>
     </row>
     <row r="157">
-      <c r="B157" t="n">
-        <v>261</v>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
       </c>
       <c r="C157" t="n">
-        <v>4</v>
+        <v>21019</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F157" t="n">
-        <v>300006</v>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>300006</t>
+        </is>
       </c>
     </row>
     <row r="158">
-      <c r="B158" t="n">
-        <v>262</v>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
       </c>
       <c r="C158" t="n">
-        <v>5</v>
+        <v>23058</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
           <t>Elation</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F158" t="n">
-        <v>300007</v>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>300007</t>
+        </is>
       </c>
     </row>
     <row r="159">
-      <c r="B159" t="n">
-        <v>263</v>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
       </c>
       <c r="C159" t="n">
-        <v>4</v>
+        <v>21055</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
           <t>Abundance</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F159" t="n">
-        <v>300008</v>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>300008</t>
+        </is>
       </c>
     </row>
     <row r="160">
-      <c r="B160" t="n">
-        <v>264</v>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
       </c>
       <c r="C160" t="n">
-        <v>4</v>
+        <v>21050</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
           <t>Remembrance</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F160" t="n">
-        <v>300009</v>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>300009</t>
+        </is>
       </c>
     </row>
     <row r="161">
-      <c r="B161" t="n">
-        <v>265</v>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
       </c>
       <c r="C161" t="n">
-        <v>3</v>
+        <v>20004</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F161" t="n">
-        <v>300010</v>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>300010</t>
+        </is>
       </c>
     </row>
     <row r="162">
-      <c r="B162" t="n">
-        <v>266</v>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
       </c>
       <c r="C162" t="n">
-        <v>4</v>
+        <v>21028</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
           <t>Abundance</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F162" t="n">
-        <v>300011</v>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>300011</t>
+        </is>
       </c>
     </row>
     <row r="163">
-      <c r="B163" t="n">
-        <v>267</v>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
       </c>
       <c r="C163" t="n">
-        <v>4</v>
+        <v>21023</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
           <t>Preservation</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F163" t="n">
-        <v>300012</v>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>300012</t>
+        </is>
       </c>
     </row>
     <row r="164">
-      <c r="B164" t="n">
-        <v>268</v>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
       </c>
       <c r="C164" t="n">
-        <v>4</v>
+        <v>21029</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F164" t="n">
-        <v>300013</v>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>300013</t>
+        </is>
       </c>
     </row>
     <row r="165">
-      <c r="B165" t="n">
-        <v>269</v>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
       </c>
       <c r="C165" t="n">
-        <v>5</v>
+        <v>23057</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
           <t>Elation</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F165" t="n">
-        <v>300014</v>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>300014</t>
+        </is>
       </c>
     </row>
     <row r="166">
-      <c r="B166" t="n">
-        <v>270</v>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
       </c>
       <c r="C166" t="n">
-        <v>4</v>
+        <v>21035</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
           <t>Abundance</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F166" t="n">
-        <v>300015</v>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>300015</t>
+        </is>
       </c>
     </row>
     <row r="167">
-      <c r="B167" t="n">
-        <v>271</v>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
       </c>
       <c r="C167" t="n">
-        <v>5</v>
+        <v>23054</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
           <t>Elation</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F167" t="n">
-        <v>300016</v>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>300016</t>
+        </is>
       </c>
     </row>
     <row r="168">
-      <c r="B168" t="n">
-        <v>272</v>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
       </c>
       <c r="C168" t="n">
-        <v>5</v>
+        <v>23025</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F168" t="n">
-        <v>310001</v>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>310001</t>
+        </is>
       </c>
     </row>
     <row r="169">
-      <c r="B169" t="n">
-        <v>273</v>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
       </c>
       <c r="C169" t="n">
-        <v>5</v>
+        <v>23047</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
           <t>Nihility</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F169" t="n">
-        <v>310002</v>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>310002</t>
+        </is>
       </c>
     </row>
     <row r="170">
-      <c r="B170" t="n">
-        <v>274</v>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
       </c>
       <c r="C170" t="n">
-        <v>4</v>
+        <v>21026</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
           <t>Destruction</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F170" t="n">
-        <v>310003</v>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>310003</t>
+        </is>
       </c>
     </row>
     <row r="171">
-      <c r="B171" t="n">
-        <v>275</v>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
       </c>
       <c r="C171" t="n">
-        <v>5</v>
+        <v>23016</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
           <t>Hunt</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F171" t="n">
-        <v>310004</v>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>310004</t>
+        </is>
       </c>
     </row>
     <row r="172">
-      <c r="B172" t="n">
-        <v>276</v>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
       </c>
       <c r="C172" t="n">
-        <v>5</v>
+        <v>23028</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
           <t>Erudition</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>MatchingPath</t>
-        </is>
-      </c>
-      <c r="F172" t="n">
-        <v>310005</v>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>MatchingPath</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>310005</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 3 to 5." promptTitle="Integer range" prompt="Enter an integer from 3 to 5." type="whole">
+      <formula1>3</formula1>
+      <formula2>5</formula2>
+    </dataValidation>
+    <dataValidation sqref="E8:E1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Destruction, Hunt, Erudition, Harmony, Nihility, Preservation, Abundance, Remembrance, Elation" promptTitle="CombatPath enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"Destruction,Hunt,Erudition,Harmony,Nihility,Preservation,Abundance,Remembrance,Elation"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F8:F1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: MatchingPath, Always, BaseStatsOnly" promptTitle="LightConeApplicability enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"MatchingPath,Always,BaseStatsOnly"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>